--- a/outputs/daily/hr_rankings_2026-08-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23.xlsx
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>62.6</v>
+        <v>63</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -910,34 +910,30 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1095,7 +1091,7 @@
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1170,7 +1166,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.9</v>
+        <v>61.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1194,7 +1190,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1218,34 +1214,30 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1403,7 +1395,7 @@
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1518,7 +1510,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.5</v>
+        <v>58</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1542,7 +1534,7 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1564,34 +1556,30 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1749,7 +1737,7 @@
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -1824,7 +1812,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.9</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1848,7 +1836,7 @@
         <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1870,34 +1858,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2055,7 +2039,7 @@
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -2130,7 +2114,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.8</v>
+        <v>54.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2154,7 +2138,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>86.40000000000001</v>
@@ -2178,34 +2162,30 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2363,7 +2343,7 @@
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -2478,7 +2458,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.8</v>
+        <v>53.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2502,7 +2482,7 @@
         <v>40.1</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2524,34 +2504,30 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2709,7 +2685,7 @@
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -2784,7 +2760,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.4</v>
+        <v>52.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2808,7 +2784,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2832,34 +2808,30 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3017,7 +2989,7 @@
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -3132,7 +3104,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3156,7 +3128,7 @@
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -3178,34 +3150,30 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3363,7 +3331,7 @@
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -3438,7 +3406,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>52.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3462,7 +3430,7 @@
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -3484,34 +3452,30 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3669,7 +3633,7 @@
       <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -3744,7 +3708,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3768,7 +3732,7 @@
         <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3790,34 +3754,30 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3975,7 +3935,7 @@
       <c r="BM11" t="inlineStr"/>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -4050,7 +4010,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.9</v>
+        <v>49.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4074,7 +4034,7 @@
         <v>40.1</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -4096,34 +4056,30 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4281,7 +4237,7 @@
       <c r="BM12" t="inlineStr"/>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -4356,7 +4312,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4380,7 +4336,7 @@
         <v>35.9</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>52.4</v>
@@ -4404,34 +4360,30 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4589,7 +4541,7 @@
       <c r="BM13" t="inlineStr"/>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -4704,7 +4656,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.2</v>
+        <v>45.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4728,7 +4680,7 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -4752,34 +4704,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4937,7 +4885,7 @@
       <c r="BM14" t="inlineStr"/>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -5052,7 +5000,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5076,7 +5024,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -5098,34 +5046,30 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5283,7 +5227,7 @@
       <c r="BM15" t="inlineStr"/>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
@@ -5358,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5382,7 +5326,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -5402,28 +5346,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5581,7 +5529,7 @@
       <c r="BM16" t="inlineStr"/>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
@@ -5656,7 +5604,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.6</v>
+        <v>40.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5680,7 +5628,7 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -5702,34 +5650,30 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5887,7 +5831,7 @@
       <c r="BM17" t="inlineStr"/>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
@@ -5962,7 +5906,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.9</v>
+        <v>39.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5986,7 +5930,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -6008,34 +5952,30 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6193,7 +6133,7 @@
       <c r="BM18" t="inlineStr"/>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
@@ -6268,7 +6208,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.7</v>
+        <v>36.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6292,7 +6232,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -6314,34 +6254,30 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6499,7 +6435,7 @@
       <c r="BM19" t="inlineStr"/>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
@@ -6980,7 +6916,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>62.6</v>
+        <v>63</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7004,7 +6940,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -7026,34 +6962,30 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7211,7 +7143,7 @@
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -7286,7 +7218,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.9</v>
+        <v>61.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7310,7 +7242,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -7334,34 +7266,30 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7519,7 +7447,7 @@
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -7634,7 +7562,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.5</v>
+        <v>58</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7658,7 +7586,7 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -7680,34 +7608,30 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7865,7 +7789,7 @@
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -7940,7 +7864,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.9</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7964,7 +7888,7 @@
         <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -7986,34 +7910,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8171,7 +8091,7 @@
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -8246,7 +8166,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.8</v>
+        <v>54.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8270,7 +8190,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>86.40000000000001</v>
@@ -8294,34 +8214,30 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8479,7 +8395,7 @@
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -8594,7 +8510,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.8</v>
+        <v>53.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8618,7 +8534,7 @@
         <v>40.1</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -8640,34 +8556,30 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8825,7 +8737,7 @@
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -8900,7 +8812,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.4</v>
+        <v>52.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8924,7 +8836,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8948,34 +8860,30 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9133,7 +9041,7 @@
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -9248,7 +9156,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9272,7 +9180,7 @@
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -9294,34 +9202,30 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9479,7 +9383,7 @@
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -9554,7 +9458,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>52.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9578,7 +9482,7 @@
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -9600,34 +9504,30 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9785,7 +9685,7 @@
       <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9860,7 +9760,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9884,7 +9784,7 @@
         <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -9906,34 +9806,30 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10091,7 +9987,7 @@
       <c r="BM11" t="inlineStr"/>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -10166,7 +10062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.9</v>
+        <v>49.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10190,7 +10086,7 @@
         <v>40.1</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -10212,34 +10108,30 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10397,7 +10289,7 @@
       <c r="BM12" t="inlineStr"/>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -10472,7 +10364,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10496,7 +10388,7 @@
         <v>35.9</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>52.4</v>
@@ -10520,34 +10412,30 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10705,7 +10593,7 @@
       <c r="BM13" t="inlineStr"/>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -10820,7 +10708,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.2</v>
+        <v>45.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10844,7 +10732,7 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -10868,34 +10756,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11053,7 +10937,7 @@
       <c r="BM14" t="inlineStr"/>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -11168,7 +11052,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11192,7 +11076,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -11214,34 +11098,30 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11399,7 +11279,7 @@
       <c r="BM15" t="inlineStr"/>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
@@ -11474,7 +11354,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11498,7 +11378,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -11518,28 +11398,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11697,7 +11581,7 @@
       <c r="BM16" t="inlineStr"/>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
@@ -11772,7 +11656,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.6</v>
+        <v>40.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11796,7 +11680,7 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -11818,34 +11702,30 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12003,7 +11883,7 @@
       <c r="BM17" t="inlineStr"/>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
@@ -12078,7 +11958,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.9</v>
+        <v>39.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12102,7 +11982,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -12124,34 +12004,30 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12309,7 +12185,7 @@
       <c r="BM18" t="inlineStr"/>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
@@ -12384,7 +12260,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.7</v>
+        <v>36.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12408,7 +12284,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -12430,34 +12306,30 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12615,7 +12487,7 @@
       <c r="BM19" t="inlineStr"/>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
